--- a/Plantilla de requerimientos.xlsx
+++ b/Plantilla de requerimientos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SDCO\Desktop\FULLSTACK2_eva2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{203444C9-F794-482C-AE54-5F6EFC393DA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE0731EB-F6B8-43E5-8814-B163F5CD57E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Historias de Usuario'!$A$1:$M$151</definedName>
   </definedNames>
   <calcPr calcId="0" iterateDelta="1E-4"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -427,15 +426,7 @@
     <t>recibir un mensaje cuando mi búsqueda no encuentre productos</t>
   </si>
   <si>
-    <t>saber que debo modificar el término de búsqueda</t>
-  </si>
-  <si>
     <t>Sprint 4</t>
-  </si>
-  <si>
-    <t>1. La funcionalidad 'Indicar cuando no hay resultados' debe estar disponible desde la sección correspondiente.
-2. Al ejecutar la acción, el sistema debe permitir al usuario recibir un mensaje cuando mi búsqueda no encuentre productos.
-3. El resultado debe permitir saber que debo modificar el término de búsqueda.</t>
   </si>
   <si>
     <t>HU-005</t>
@@ -473,11 +464,6 @@
     <t>Sprint 6</t>
   </si>
   <si>
-    <t>1. La funcionalidad 'Buscar sin distinguir mayúsculas' debe estar disponible desde la sección correspondiente.
-2. Al ejecutar la acción, el sistema debe permitir al usuario realizar búsquedas sin importar si escribo mayúsculas o minúsculas.
-3. El resultado debe permitir obtener resultados de forma más flexible.</t>
-  </si>
-  <si>
     <t>HU-007</t>
   </si>
   <si>
@@ -513,11 +499,6 @@
     <t>Sprint 8</t>
   </si>
   <si>
-    <t>1. La funcionalidad 'Actualizar resultados al buscar' debe estar disponible desde la sección correspondiente.
-2. Al ejecutar la acción, el sistema debe permitir al usuario ver los resultados actualizados después de modificar mi búsqueda.
-3. El resultado debe permitir evitar información desactualizada en pantalla.</t>
-  </si>
-  <si>
     <t>HU-009</t>
   </si>
   <si>
@@ -1092,11 +1073,6 @@
     <t>evitar errores en mi selección</t>
   </si>
   <si>
-    <t>1. La funcionalidad 'Evitar cantidades inválidas' debe estar disponible desde la sección correspondiente.
-2. Al ejecutar la acción, el sistema debe permitir al usuario recibir una validación al ingresar una cantidad no permitida.
-3. El resultado debe permitir evitar errores en mi selección.</t>
-  </si>
-  <si>
     <t>HU-042</t>
   </si>
   <si>
@@ -1387,11 +1363,6 @@
     <t>evitar valores incorrectos en la interfaz</t>
   </si>
   <si>
-    <t>1. La funcionalidad 'Evitar contador negativo' debe estar disponible desde la sección correspondiente.
-2. Al ejecutar la acción, el sistema debe permitir al usuario mantener el contador en cero como mínimo.
-3. El resultado debe permitir evitar valores incorrectos en la interfaz.</t>
-  </si>
-  <si>
     <t>HU-059</t>
   </si>
   <si>
@@ -1967,11 +1938,6 @@
   </si>
   <si>
     <t>saber que mi cuenta fue creada</t>
-  </si>
-  <si>
-    <t>1. La funcionalidad 'Confirmar registro exitoso' debe estar disponible desde la sección correspondiente.
-2. Al ejecutar la acción, el sistema debe permitir al usuario recibir un mensaje visual cuando mi registro se complete correctamente.
-3. El resultado debe permitir saber que mi cuenta fue creada.</t>
   </si>
   <si>
     <t>Historia asociada a EP-07. Requiere validación funcional y visual antes de pasar a desarrollo.</t>
@@ -3088,6 +3054,153 @@
         <charset val="1"/>
       </rPr>
       <t>3. El resultado debe permitir preparar una compra con los productos que deseo.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. La funcionalidad 'Indicar cuando no hay resultados' debe estar disponible desde la sección correspondiente.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>2. Al ejecutar la acción, el sistema debe permitir al usuario recibir un mensaje cuando mi búsqueda no encuentre productos.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+3. El resultado debe permitir saber que debo modificar el término de búsqueda.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. La funcionalidad 'Actualizar resultados al buscar' debe estar disponible desde la sección correspondiente.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>2. Al ejecutar la acción, el sistema debe permitir al usuario ver los resultados actualizados después de modificar mi búsqueda.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+3. El resultado debe permitir evitar información desactualizada en pantalla.</t>
+    </r>
+  </si>
+  <si>
+    <t>z</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. La funcionalidad 'Evitar cantidades inválidas' debe estar disponible desde la sección correspondiente.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>2. Al ejecutar la acción, el sistema debe permitir al usuario recibir una validación al ingresar una cantidad no permitida.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+3. El resultado debe permitir evitar errores en mi selección.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. La funcionalidad 'Confirmar registro exitoso' debe estar disponible desde la sección correspondiente.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>2. Al ejecutar la acción, el sistema debe permitir al usuario recibir un mensaje visual cuando mi registro se complete correctamente.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+3. El resultado debe permitir saber que mi cuenta fue creada.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. La funcionalidad 'Evitar contador negativo' debe estar disponible desde la sección correspondiente.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>2. Al ejecutar la acción, el sistema debe permitir al usuario mantener el contador en cero como mínimo.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+3. El resultado debe permitir evitar valores incorrectos en la interfaz.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. La funcionalidad 'Buscar sin distinguir mayúsculas' debe estar disponible desde la sección correspondiente.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>2. Al ejecutar la acción, el sistema debe permitir al usuario realizar búsquedas sin importar si escribo mayúsculas o minúsculas.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+3. El resultado debe permitir obtener resultados de forma más flexible.</t>
     </r>
   </si>
 </sst>
@@ -5218,17 +5331,17 @@
       <c r="E5" t="s">
         <v>128</v>
       </c>
-      <c r="F5" t="s">
-        <v>129</v>
+      <c r="F5" s="14" t="s">
+        <v>888</v>
       </c>
       <c r="G5" t="s">
         <v>62</v>
       </c>
       <c r="H5" t="s">
-        <v>130</v>
-      </c>
-      <c r="I5" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>886</v>
       </c>
       <c r="J5" t="s">
         <v>45</v>
@@ -5245,31 +5358,31 @@
     </row>
     <row r="6" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B6" t="s">
         <v>103</v>
       </c>
       <c r="C6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D6" t="s">
         <v>105</v>
       </c>
       <c r="E6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G6" t="s">
         <v>62</v>
       </c>
       <c r="H6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="J6" t="s">
         <v>45</v>
@@ -5286,31 +5399,31 @@
     </row>
     <row r="7" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B7" t="s">
         <v>103</v>
       </c>
       <c r="C7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D7" t="s">
         <v>105</v>
       </c>
       <c r="E7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G7" t="s">
         <v>62</v>
       </c>
       <c r="H7" t="s">
-        <v>142</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>143</v>
+        <v>140</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>892</v>
       </c>
       <c r="J7" t="s">
         <v>45</v>
@@ -5327,31 +5440,31 @@
     </row>
     <row r="8" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B8" t="s">
         <v>103</v>
       </c>
       <c r="C8" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D8" t="s">
         <v>105</v>
       </c>
       <c r="E8" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F8" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G8" t="s">
         <v>44</v>
       </c>
       <c r="H8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="J8" t="s">
         <v>45</v>
@@ -5368,31 +5481,31 @@
     </row>
     <row r="9" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B9" t="s">
         <v>103</v>
       </c>
       <c r="C9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D9" t="s">
         <v>105</v>
       </c>
-      <c r="E9" t="s">
-        <v>152</v>
+      <c r="E9" s="14" t="s">
+        <v>149</v>
       </c>
       <c r="F9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G9" t="s">
         <v>44</v>
       </c>
       <c r="H9" t="s">
-        <v>154</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>155</v>
+        <v>151</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>887</v>
       </c>
       <c r="J9" t="s">
         <v>45</v>
@@ -5409,31 +5522,31 @@
     </row>
     <row r="10" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B10" t="s">
         <v>103</v>
       </c>
       <c r="C10" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D10" t="s">
         <v>105</v>
       </c>
       <c r="E10" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F10" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G10" t="s">
         <v>93</v>
       </c>
       <c r="H10" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="J10" t="s">
         <v>45</v>
@@ -5450,31 +5563,31 @@
     </row>
     <row r="11" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B11" t="s">
         <v>103</v>
       </c>
       <c r="C11" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D11" t="s">
         <v>105</v>
       </c>
       <c r="E11" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F11" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="G11" t="s">
         <v>93</v>
       </c>
       <c r="H11" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="J11" t="s">
         <v>45</v>
@@ -5491,31 +5604,31 @@
     </row>
     <row r="12" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B12" t="s">
         <v>103</v>
       </c>
       <c r="C12" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D12" t="s">
         <v>105</v>
       </c>
       <c r="E12" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F12" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="G12" t="s">
         <v>44</v>
       </c>
       <c r="H12" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="J12" t="s">
         <v>45</v>
@@ -5532,31 +5645,31 @@
     </row>
     <row r="13" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B13" t="s">
         <v>103</v>
       </c>
       <c r="C13" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D13" t="s">
         <v>105</v>
       </c>
       <c r="E13" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F13" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="G13" t="s">
         <v>93</v>
       </c>
       <c r="H13" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="J13" t="s">
         <v>45</v>
@@ -5573,31 +5686,31 @@
     </row>
     <row r="14" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B14" t="s">
         <v>103</v>
       </c>
       <c r="C14" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D14" t="s">
         <v>105</v>
       </c>
       <c r="E14" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F14" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="G14" t="s">
         <v>62</v>
       </c>
       <c r="H14" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="J14" t="s">
         <v>45</v>
@@ -5614,31 +5727,31 @@
     </row>
     <row r="15" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B15" t="s">
         <v>103</v>
       </c>
       <c r="C15" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D15" t="s">
         <v>105</v>
       </c>
       <c r="E15" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F15" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="G15" t="s">
         <v>44</v>
       </c>
       <c r="H15" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="J15" t="s">
         <v>45</v>
@@ -5655,31 +5768,31 @@
     </row>
     <row r="16" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B16" t="s">
         <v>103</v>
       </c>
-      <c r="C16" t="s">
-        <v>193</v>
+      <c r="C16" s="14" t="s">
+        <v>189</v>
       </c>
       <c r="D16" t="s">
         <v>105</v>
       </c>
       <c r="E16" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="F16" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="G16" t="s">
         <v>93</v>
       </c>
       <c r="H16" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="J16" t="s">
         <v>45</v>
@@ -5696,22 +5809,22 @@
     </row>
     <row r="17" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C17" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D17" t="s">
         <v>105</v>
       </c>
       <c r="E17" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F17" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="G17" t="s">
         <v>44</v>
@@ -5720,7 +5833,7 @@
         <v>108</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="J17" t="s">
         <v>45</v>
@@ -5732,27 +5845,27 @@
         <v>110</v>
       </c>
       <c r="M17" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B18" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C18" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D18" t="s">
         <v>105</v>
       </c>
       <c r="E18" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F18" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="G18" t="s">
         <v>44</v>
@@ -5761,7 +5874,7 @@
         <v>116</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="J18" t="s">
         <v>45</v>
@@ -5773,27 +5886,27 @@
         <v>118</v>
       </c>
       <c r="M18" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B19" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C19" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D19" t="s">
         <v>105</v>
       </c>
       <c r="E19" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="F19" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="G19" t="s">
         <v>44</v>
@@ -5802,7 +5915,7 @@
         <v>123</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="J19" t="s">
         <v>45</v>
@@ -5814,36 +5927,36 @@
         <v>125</v>
       </c>
       <c r="M19" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B20" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C20" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D20" t="s">
         <v>105</v>
       </c>
       <c r="E20" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="F20" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="G20" t="s">
         <v>44</v>
       </c>
       <c r="H20" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="J20" t="s">
         <v>45</v>
@@ -5855,36 +5968,36 @@
         <v>110</v>
       </c>
       <c r="M20" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B21" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C21" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D21" t="s">
         <v>105</v>
       </c>
       <c r="E21" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F21" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="G21" t="s">
         <v>44</v>
       </c>
       <c r="H21" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="J21" t="s">
         <v>45</v>
@@ -5896,36 +6009,36 @@
         <v>118</v>
       </c>
       <c r="M21" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B22" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C22" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D22" t="s">
         <v>105</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="F22" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="G22" t="s">
         <v>62</v>
       </c>
       <c r="H22" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="J22" t="s">
         <v>45</v>
@@ -5937,36 +6050,36 @@
         <v>125</v>
       </c>
       <c r="M22" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B23" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D23" t="s">
         <v>105</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="F23" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="G23" t="s">
         <v>62</v>
       </c>
       <c r="H23" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="J23" t="s">
         <v>45</v>
@@ -5978,36 +6091,36 @@
         <v>110</v>
       </c>
       <c r="M23" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B24" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C24" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D24" t="s">
         <v>105</v>
       </c>
       <c r="E24" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="F24" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G24" t="s">
         <v>62</v>
       </c>
       <c r="H24" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="J24" t="s">
         <v>45</v>
@@ -6019,36 +6132,36 @@
         <v>118</v>
       </c>
       <c r="M24" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B25" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C25" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D25" t="s">
         <v>105</v>
       </c>
       <c r="E25" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F25" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G25" t="s">
         <v>44</v>
       </c>
       <c r="H25" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>890</v>
+        <v>883</v>
       </c>
       <c r="J25" t="s">
         <v>45</v>
@@ -6060,36 +6173,36 @@
         <v>125</v>
       </c>
       <c r="M25" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B26" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C26" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="D26" t="s">
         <v>105</v>
       </c>
       <c r="E26" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="F26" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="G26" t="s">
         <v>44</v>
       </c>
       <c r="H26" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="J26" t="s">
         <v>45</v>
@@ -6101,36 +6214,36 @@
         <v>110</v>
       </c>
       <c r="M26" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B27" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C27" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="D27" t="s">
         <v>105</v>
       </c>
       <c r="E27" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F27" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="G27" t="s">
         <v>62</v>
       </c>
       <c r="H27" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="I27" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="J27" t="s">
         <v>45</v>
@@ -6142,36 +6255,36 @@
         <v>118</v>
       </c>
       <c r="M27" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B28" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C28" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="D28" t="s">
         <v>105</v>
       </c>
       <c r="E28" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="F28" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="G28" t="s">
         <v>44</v>
       </c>
       <c r="H28" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="I28" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="J28" t="s">
         <v>45</v>
@@ -6183,36 +6296,36 @@
         <v>125</v>
       </c>
       <c r="M28" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B29" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C29" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="D29" t="s">
         <v>105</v>
       </c>
       <c r="E29" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="F29" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="G29" t="s">
         <v>93</v>
       </c>
       <c r="H29" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I29" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="J29" t="s">
         <v>45</v>
@@ -6224,36 +6337,36 @@
         <v>110</v>
       </c>
       <c r="M29" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B30" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C30" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
         <v>105</v>
       </c>
       <c r="E30" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="F30" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="G30" t="s">
         <v>62</v>
       </c>
       <c r="H30" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="I30" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="J30" t="s">
         <v>45</v>
@@ -6265,36 +6378,36 @@
         <v>118</v>
       </c>
       <c r="M30" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B31" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C31" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D31" t="s">
         <v>105</v>
       </c>
       <c r="E31" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="F31" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="G31" t="s">
         <v>62</v>
       </c>
       <c r="H31" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="I31" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="J31" t="s">
         <v>45</v>
@@ -6306,27 +6419,27 @@
         <v>125</v>
       </c>
       <c r="M31" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B32" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="D32" t="s">
         <v>105</v>
       </c>
       <c r="E32" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="F32" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="G32" t="s">
         <v>44</v>
@@ -6335,7 +6448,7 @@
         <v>108</v>
       </c>
       <c r="I32" s="13" t="s">
-        <v>892</v>
+        <v>885</v>
       </c>
       <c r="J32" t="s">
         <v>45</v>
@@ -6347,27 +6460,27 @@
         <v>110</v>
       </c>
       <c r="M32" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B33" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C33" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="D33" t="s">
         <v>105</v>
       </c>
       <c r="E33" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="F33" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="G33" t="s">
         <v>44</v>
@@ -6376,7 +6489,7 @@
         <v>116</v>
       </c>
       <c r="I33" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="J33" t="s">
         <v>45</v>
@@ -6388,27 +6501,27 @@
         <v>118</v>
       </c>
       <c r="M33" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B34" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C34" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D34" t="s">
         <v>105</v>
       </c>
       <c r="E34" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F34" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G34" t="s">
         <v>44</v>
@@ -6417,7 +6530,7 @@
         <v>123</v>
       </c>
       <c r="I34" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="J34" t="s">
         <v>45</v>
@@ -6429,36 +6542,36 @@
         <v>125</v>
       </c>
       <c r="M34" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B35" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C35" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="D35" t="s">
         <v>105</v>
       </c>
       <c r="E35" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="F35" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="G35" t="s">
         <v>44</v>
       </c>
       <c r="H35" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I35" s="13" t="s">
-        <v>891</v>
+        <v>884</v>
       </c>
       <c r="J35" t="s">
         <v>45</v>
@@ -6470,36 +6583,36 @@
         <v>110</v>
       </c>
       <c r="M35" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B36" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C36" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D36" t="s">
         <v>105</v>
       </c>
       <c r="E36" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="F36" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="G36" t="s">
         <v>44</v>
       </c>
       <c r="H36" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I36" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="J36" t="s">
         <v>45</v>
@@ -6511,36 +6624,36 @@
         <v>118</v>
       </c>
       <c r="M36" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B37" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C37" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="D37" t="s">
         <v>105</v>
       </c>
       <c r="E37" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="F37" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="G37" t="s">
         <v>44</v>
       </c>
       <c r="H37" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I37" s="12" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="J37" t="s">
         <v>45</v>
@@ -6552,36 +6665,36 @@
         <v>125</v>
       </c>
       <c r="M37" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B38" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C38" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D38" t="s">
         <v>105</v>
       </c>
       <c r="E38" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="F38" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="G38" t="s">
         <v>62</v>
       </c>
       <c r="H38" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I38" s="12" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="J38" t="s">
         <v>45</v>
@@ -6593,36 +6706,36 @@
         <v>110</v>
       </c>
       <c r="M38" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B39" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C39" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D39" t="s">
         <v>105</v>
       </c>
       <c r="E39" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="F39" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G39" t="s">
         <v>44</v>
       </c>
       <c r="H39" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I39" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="J39" t="s">
         <v>45</v>
@@ -6634,36 +6747,36 @@
         <v>118</v>
       </c>
       <c r="M39" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B40" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C40" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D40" t="s">
         <v>105</v>
       </c>
       <c r="E40" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="F40" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="G40" t="s">
         <v>44</v>
       </c>
       <c r="H40" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I40" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="J40" t="s">
         <v>45</v>
@@ -6675,36 +6788,36 @@
         <v>125</v>
       </c>
       <c r="M40" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B41" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C41" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D41" t="s">
         <v>105</v>
       </c>
       <c r="E41" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="F41" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="G41" t="s">
         <v>62</v>
       </c>
       <c r="H41" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="I41" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="J41" t="s">
         <v>45</v>
@@ -6716,36 +6829,36 @@
         <v>110</v>
       </c>
       <c r="M41" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="B42" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C42" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D42" t="s">
         <v>105</v>
       </c>
       <c r="E42" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F42" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="G42" t="s">
         <v>44</v>
       </c>
       <c r="H42" t="s">
-        <v>172</v>
-      </c>
-      <c r="I42" t="s">
-        <v>328</v>
+        <v>168</v>
+      </c>
+      <c r="I42" s="13" t="s">
+        <v>889</v>
       </c>
       <c r="J42" t="s">
         <v>45</v>
@@ -6757,36 +6870,36 @@
         <v>118</v>
       </c>
       <c r="M42" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="B43" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C43" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="D43" t="s">
         <v>105</v>
       </c>
       <c r="E43" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="F43" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="G43" t="s">
         <v>62</v>
       </c>
       <c r="H43" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="I43" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J43" t="s">
         <v>45</v>
@@ -6798,36 +6911,36 @@
         <v>125</v>
       </c>
       <c r="M43" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="B44" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C44" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="D44" t="s">
         <v>105</v>
       </c>
       <c r="E44" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="F44" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="G44" t="s">
         <v>44</v>
       </c>
       <c r="H44" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I44" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="J44" t="s">
         <v>45</v>
@@ -6839,36 +6952,36 @@
         <v>110</v>
       </c>
       <c r="M44" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="B45" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C45" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="D45" t="s">
         <v>105</v>
       </c>
       <c r="E45" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="F45" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="G45" t="s">
         <v>44</v>
       </c>
       <c r="H45" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="I45" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="J45" t="s">
         <v>45</v>
@@ -6880,36 +6993,36 @@
         <v>118</v>
       </c>
       <c r="M45" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="B46" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C46" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="D46" t="s">
         <v>105</v>
       </c>
       <c r="E46" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="F46" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="G46" t="s">
         <v>44</v>
       </c>
       <c r="H46" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="I46" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="J46" t="s">
         <v>45</v>
@@ -6921,27 +7034,27 @@
         <v>125</v>
       </c>
       <c r="M46" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="B47" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C47" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="D47" t="s">
         <v>105</v>
       </c>
       <c r="E47" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="F47" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="G47" t="s">
         <v>44</v>
@@ -6950,7 +7063,7 @@
         <v>108</v>
       </c>
       <c r="I47" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="J47" t="s">
         <v>45</v>
@@ -6962,27 +7075,27 @@
         <v>110</v>
       </c>
       <c r="M47" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="B48" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C48" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="D48" t="s">
         <v>105</v>
       </c>
       <c r="E48" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="F48" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="G48" t="s">
         <v>44</v>
@@ -6991,7 +7104,7 @@
         <v>116</v>
       </c>
       <c r="I48" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="J48" t="s">
         <v>45</v>
@@ -7003,27 +7116,27 @@
         <v>118</v>
       </c>
       <c r="M48" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
     </row>
     <row r="49" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="B49" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C49" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="D49" t="s">
         <v>105</v>
       </c>
       <c r="E49" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="F49" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="G49" t="s">
         <v>44</v>
@@ -7032,7 +7145,7 @@
         <v>123</v>
       </c>
       <c r="I49" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="J49" t="s">
         <v>45</v>
@@ -7044,36 +7157,36 @@
         <v>125</v>
       </c>
       <c r="M49" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="B50" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C50" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="D50" t="s">
         <v>105</v>
       </c>
       <c r="E50" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="F50" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="G50" t="s">
         <v>44</v>
       </c>
       <c r="H50" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I50" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="J50" t="s">
         <v>45</v>
@@ -7085,36 +7198,36 @@
         <v>110</v>
       </c>
       <c r="M50" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="B51" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C51" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="D51" t="s">
         <v>105</v>
       </c>
       <c r="E51" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="F51" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="G51" t="s">
         <v>62</v>
       </c>
       <c r="H51" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I51" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="J51" t="s">
         <v>45</v>
@@ -7126,36 +7239,36 @@
         <v>118</v>
       </c>
       <c r="M51" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="B52" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C52" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="D52" t="s">
         <v>105</v>
       </c>
       <c r="E52" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="F52" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="G52" t="s">
         <v>62</v>
       </c>
       <c r="H52" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I52" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="J52" t="s">
         <v>45</v>
@@ -7167,36 +7280,36 @@
         <v>125</v>
       </c>
       <c r="M52" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="B53" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C53" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D53" t="s">
         <v>105</v>
       </c>
       <c r="E53" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="F53" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="G53" t="s">
         <v>44</v>
       </c>
       <c r="H53" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I53" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="J53" t="s">
         <v>45</v>
@@ -7208,36 +7321,36 @@
         <v>110</v>
       </c>
       <c r="M53" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="B54" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C54" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="D54" t="s">
         <v>105</v>
       </c>
       <c r="E54" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="F54" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="G54" t="s">
         <v>44</v>
       </c>
       <c r="H54" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I54" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="J54" t="s">
         <v>45</v>
@@ -7249,36 +7362,36 @@
         <v>118</v>
       </c>
       <c r="M54" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="B55" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C55" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="D55" t="s">
         <v>105</v>
       </c>
       <c r="E55" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="F55" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="G55" t="s">
         <v>93</v>
       </c>
       <c r="H55" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I55" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="J55" t="s">
         <v>45</v>
@@ -7290,36 +7403,36 @@
         <v>125</v>
       </c>
       <c r="M55" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
     </row>
     <row r="56" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="B56" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C56" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="D56" t="s">
         <v>105</v>
       </c>
       <c r="E56" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="F56" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="G56" t="s">
         <v>44</v>
       </c>
       <c r="H56" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="I56" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="J56" t="s">
         <v>45</v>
@@ -7331,36 +7444,36 @@
         <v>110</v>
       </c>
       <c r="M56" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="B57" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C57" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="D57" t="s">
         <v>105</v>
       </c>
       <c r="E57" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="F57" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="G57" t="s">
         <v>62</v>
       </c>
       <c r="H57" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="I57" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="J57" t="s">
         <v>45</v>
@@ -7372,36 +7485,36 @@
         <v>118</v>
       </c>
       <c r="M57" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="B58" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C58" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="D58" t="s">
         <v>105</v>
       </c>
       <c r="E58" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="F58" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="G58" t="s">
         <v>62</v>
       </c>
       <c r="H58" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="I58" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="J58" t="s">
         <v>45</v>
@@ -7413,36 +7526,36 @@
         <v>125</v>
       </c>
       <c r="M58" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B59" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C59" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="D59" t="s">
         <v>105</v>
       </c>
       <c r="E59" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="F59" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="G59" t="s">
         <v>44</v>
       </c>
       <c r="H59" t="s">
-        <v>184</v>
-      </c>
-      <c r="I59" t="s">
-        <v>415</v>
+        <v>180</v>
+      </c>
+      <c r="I59" s="13" t="s">
+        <v>891</v>
       </c>
       <c r="J59" t="s">
         <v>45</v>
@@ -7454,36 +7567,36 @@
         <v>110</v>
       </c>
       <c r="M59" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="B60" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C60" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="D60" t="s">
         <v>105</v>
       </c>
       <c r="E60" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="F60" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="G60" t="s">
         <v>93</v>
       </c>
       <c r="H60" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="I60" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="J60" t="s">
         <v>45</v>
@@ -7495,36 +7608,36 @@
         <v>118</v>
       </c>
       <c r="M60" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="B61" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C61" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="D61" t="s">
         <v>105</v>
       </c>
       <c r="E61" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="F61" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="G61" t="s">
         <v>44</v>
       </c>
       <c r="H61" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="I61" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="J61" t="s">
         <v>45</v>
@@ -7536,27 +7649,27 @@
         <v>125</v>
       </c>
       <c r="M61" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="B62" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C62" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="D62" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="E62" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="F62" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="G62" t="s">
         <v>44</v>
@@ -7565,7 +7678,7 @@
         <v>108</v>
       </c>
       <c r="I62" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="J62" t="s">
         <v>45</v>
@@ -7577,27 +7690,27 @@
         <v>110</v>
       </c>
       <c r="M62" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="B63" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C63" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="D63" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="E63" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="F63" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="G63" t="s">
         <v>44</v>
@@ -7606,7 +7719,7 @@
         <v>116</v>
       </c>
       <c r="I63" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="J63" t="s">
         <v>45</v>
@@ -7618,27 +7731,27 @@
         <v>118</v>
       </c>
       <c r="M63" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="B64" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C64" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="D64" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="E64" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="F64" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="G64" t="s">
         <v>44</v>
@@ -7647,7 +7760,7 @@
         <v>123</v>
       </c>
       <c r="I64" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="J64" t="s">
         <v>45</v>
@@ -7659,36 +7772,36 @@
         <v>125</v>
       </c>
       <c r="M64" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="B65" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C65" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="D65" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="E65" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="F65" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="G65" t="s">
         <v>62</v>
       </c>
       <c r="H65" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I65" s="12" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="J65" t="s">
         <v>45</v>
@@ -7700,36 +7813,36 @@
         <v>110</v>
       </c>
       <c r="M65" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="B66" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C66" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="D66" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="E66" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="F66" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="G66" t="s">
         <v>62</v>
       </c>
       <c r="H66" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I66" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="J66" t="s">
         <v>45</v>
@@ -7741,36 +7854,36 @@
         <v>118</v>
       </c>
       <c r="M66" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
     </row>
     <row r="67" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="B67" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C67" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D67" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="E67" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="F67" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="G67" t="s">
         <v>62</v>
       </c>
       <c r="H67" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I67" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="J67" t="s">
         <v>45</v>
@@ -7782,36 +7895,36 @@
         <v>125</v>
       </c>
       <c r="M67" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
     </row>
     <row r="68" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="B68" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C68" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="D68" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="E68" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="F68" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="G68" t="s">
         <v>44</v>
       </c>
       <c r="H68" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I68" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="J68" t="s">
         <v>45</v>
@@ -7823,36 +7936,36 @@
         <v>110</v>
       </c>
       <c r="M68" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
     </row>
     <row r="69" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="B69" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C69" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="D69" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="E69" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="F69" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="G69" t="s">
         <v>93</v>
       </c>
       <c r="H69" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I69" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="J69" t="s">
         <v>45</v>
@@ -7864,36 +7977,36 @@
         <v>118</v>
       </c>
       <c r="M69" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="B70" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C70" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="D70" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="E70" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="F70" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="G70" t="s">
         <v>62</v>
       </c>
       <c r="H70" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I70" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="J70" t="s">
         <v>45</v>
@@ -7905,36 +8018,36 @@
         <v>125</v>
       </c>
       <c r="M70" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="B71" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C71" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="D71" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="E71" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="F71" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="G71" t="s">
         <v>44</v>
       </c>
       <c r="H71" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="I71" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="J71" t="s">
         <v>45</v>
@@ -7946,36 +8059,36 @@
         <v>110</v>
       </c>
       <c r="M71" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
     </row>
     <row r="72" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="B72" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C72" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="D72" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="E72" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="F72" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="G72" t="s">
         <v>62</v>
       </c>
       <c r="H72" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="I72" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="J72" t="s">
         <v>45</v>
@@ -7987,36 +8100,36 @@
         <v>118</v>
       </c>
       <c r="M72" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
     </row>
     <row r="73" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="B73" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C73" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="D73" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="E73" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="F73" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="G73" t="s">
         <v>44</v>
       </c>
       <c r="H73" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="I73" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="J73" t="s">
         <v>45</v>
@@ -8028,36 +8141,36 @@
         <v>125</v>
       </c>
       <c r="M73" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
     </row>
     <row r="74" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="B74" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C74" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="D74" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="E74" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="F74" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="G74" t="s">
         <v>44</v>
       </c>
       <c r="H74" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I74" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="J74" t="s">
         <v>45</v>
@@ -8069,36 +8182,36 @@
         <v>110</v>
       </c>
       <c r="M74" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
     </row>
     <row r="75" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="B75" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C75" s="14" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="D75" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="E75" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="F75" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="G75" t="s">
         <v>62</v>
       </c>
       <c r="H75" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="I75" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="J75" t="s">
         <v>45</v>
@@ -8110,36 +8223,36 @@
         <v>118</v>
       </c>
       <c r="M75" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
     </row>
     <row r="76" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="B76" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C76" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="D76" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="E76" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="F76" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="G76" t="s">
         <v>93</v>
       </c>
       <c r="H76" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="I76" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="J76" t="s">
         <v>45</v>
@@ -8151,27 +8264,27 @@
         <v>125</v>
       </c>
       <c r="M76" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
     </row>
     <row r="77" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B77" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="C77" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="D77" t="s">
         <v>105</v>
       </c>
       <c r="E77" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="F77" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="G77" t="s">
         <v>44</v>
@@ -8180,7 +8293,7 @@
         <v>108</v>
       </c>
       <c r="I77" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="J77" t="s">
         <v>45</v>
@@ -8192,27 +8305,27 @@
         <v>110</v>
       </c>
       <c r="M77" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
     </row>
     <row r="78" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="B78" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="C78" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="D78" t="s">
         <v>105</v>
       </c>
       <c r="E78" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="F78" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="G78" t="s">
         <v>44</v>
@@ -8221,7 +8334,7 @@
         <v>116</v>
       </c>
       <c r="I78" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="J78" t="s">
         <v>45</v>
@@ -8233,27 +8346,27 @@
         <v>118</v>
       </c>
       <c r="M78" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
     </row>
     <row r="79" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="B79" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="C79" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="D79" t="s">
         <v>105</v>
       </c>
       <c r="E79" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="F79" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="G79" t="s">
         <v>44</v>
@@ -8262,7 +8375,7 @@
         <v>123</v>
       </c>
       <c r="I79" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="J79" t="s">
         <v>45</v>
@@ -8274,36 +8387,36 @@
         <v>125</v>
       </c>
       <c r="M79" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
     </row>
     <row r="80" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="B80" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="C80" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="D80" t="s">
         <v>105</v>
       </c>
       <c r="E80" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="F80" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="G80" t="s">
         <v>44</v>
       </c>
       <c r="H80" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I80" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="J80" t="s">
         <v>45</v>
@@ -8315,36 +8428,36 @@
         <v>110</v>
       </c>
       <c r="M80" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
     </row>
     <row r="81" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="B81" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="C81" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="D81" t="s">
         <v>105</v>
       </c>
       <c r="E81" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="F81" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="G81" t="s">
         <v>62</v>
       </c>
       <c r="H81" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I81" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="J81" t="s">
         <v>45</v>
@@ -8356,36 +8469,36 @@
         <v>118</v>
       </c>
       <c r="M81" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
     </row>
     <row r="82" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="B82" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="C82" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="D82" t="s">
         <v>105</v>
       </c>
       <c r="E82" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="F82" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="G82" t="s">
         <v>62</v>
       </c>
       <c r="H82" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I82" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="J82" t="s">
         <v>45</v>
@@ -8397,36 +8510,36 @@
         <v>125</v>
       </c>
       <c r="M82" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="B83" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="C83" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="D83" t="s">
         <v>105</v>
       </c>
       <c r="E83" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="F83" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="G83" t="s">
         <v>62</v>
       </c>
       <c r="H83" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I83" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="J83" t="s">
         <v>45</v>
@@ -8438,36 +8551,36 @@
         <v>110</v>
       </c>
       <c r="M83" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
     </row>
     <row r="84" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="B84" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="C84" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="D84" t="s">
         <v>105</v>
       </c>
       <c r="E84" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="F84" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="G84" t="s">
         <v>44</v>
       </c>
       <c r="H84" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I84" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="J84" t="s">
         <v>45</v>
@@ -8479,36 +8592,36 @@
         <v>118</v>
       </c>
       <c r="M84" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="B85" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="C85" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="D85" t="s">
         <v>105</v>
       </c>
       <c r="E85" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="F85" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="G85" t="s">
         <v>62</v>
       </c>
       <c r="H85" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I85" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="J85" t="s">
         <v>45</v>
@@ -8520,36 +8633,36 @@
         <v>125</v>
       </c>
       <c r="M85" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="B86" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="C86" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="D86" t="s">
         <v>105</v>
       </c>
       <c r="E86" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="F86" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="G86" t="s">
         <v>44</v>
       </c>
       <c r="H86" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="I86" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="J86" t="s">
         <v>45</v>
@@ -8561,36 +8674,36 @@
         <v>110</v>
       </c>
       <c r="M86" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
     </row>
     <row r="87" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="B87" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="C87" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="D87" t="s">
         <v>105</v>
       </c>
       <c r="E87" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="F87" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="G87" t="s">
         <v>44</v>
       </c>
       <c r="H87" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="I87" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="J87" t="s">
         <v>45</v>
@@ -8602,36 +8715,36 @@
         <v>118</v>
       </c>
       <c r="M87" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
     </row>
     <row r="88" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="B88" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="C88" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="D88" t="s">
         <v>105</v>
       </c>
       <c r="E88" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="F88" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="G88" t="s">
         <v>44</v>
       </c>
       <c r="H88" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="I88" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="J88" t="s">
         <v>45</v>
@@ -8643,36 +8756,36 @@
         <v>125</v>
       </c>
       <c r="M88" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
     </row>
     <row r="89" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="B89" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="C89" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="D89" t="s">
         <v>105</v>
       </c>
       <c r="E89" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="F89" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="G89" t="s">
         <v>44</v>
       </c>
       <c r="H89" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I89" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="J89" t="s">
         <v>45</v>
@@ -8684,36 +8797,36 @@
         <v>110</v>
       </c>
       <c r="M89" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
     </row>
     <row r="90" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="B90" t="s">
-        <v>505</v>
-      </c>
-      <c r="C90" t="s">
-        <v>572</v>
+        <v>499</v>
+      </c>
+      <c r="C90" s="14" t="s">
+        <v>566</v>
       </c>
       <c r="D90" t="s">
         <v>105</v>
       </c>
       <c r="E90" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="F90" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="G90" t="s">
         <v>62</v>
       </c>
       <c r="H90" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="I90" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="J90" t="s">
         <v>45</v>
@@ -8725,36 +8838,36 @@
         <v>118</v>
       </c>
       <c r="M90" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
     </row>
     <row r="91" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="B91" t="s">
-        <v>505</v>
-      </c>
-      <c r="C91" t="s">
-        <v>577</v>
+        <v>499</v>
+      </c>
+      <c r="C91" s="14" t="s">
+        <v>571</v>
       </c>
       <c r="D91" t="s">
         <v>105</v>
       </c>
       <c r="E91" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="F91" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="G91" t="s">
         <v>62</v>
       </c>
       <c r="H91" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="I91" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="J91" t="s">
         <v>45</v>
@@ -8766,27 +8879,27 @@
         <v>125</v>
       </c>
       <c r="M91" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
     </row>
     <row r="92" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="B92" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="C92" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="D92" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="E92" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="F92" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="G92" t="s">
         <v>44</v>
@@ -8794,8 +8907,8 @@
       <c r="H92" t="s">
         <v>108</v>
       </c>
-      <c r="I92" t="s">
-        <v>587</v>
+      <c r="I92" s="13" t="s">
+        <v>890</v>
       </c>
       <c r="J92" t="s">
         <v>45</v>
@@ -8807,27 +8920,27 @@
         <v>110</v>
       </c>
       <c r="M92" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
     </row>
     <row r="93" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="B93" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="C93" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="D93" t="s">
+        <v>578</v>
+      </c>
+      <c r="E93" t="s">
         <v>584</v>
       </c>
-      <c r="E93" t="s">
-        <v>591</v>
-      </c>
       <c r="F93" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="G93" t="s">
         <v>44</v>
@@ -8836,7 +8949,7 @@
         <v>116</v>
       </c>
       <c r="I93" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="J93" t="s">
         <v>45</v>
@@ -8848,27 +8961,27 @@
         <v>118</v>
       </c>
       <c r="M93" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
     </row>
     <row r="94" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="B94" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="C94" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="D94" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="E94" s="14" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="F94" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="G94" t="s">
         <v>44</v>
@@ -8877,7 +8990,7 @@
         <v>123</v>
       </c>
       <c r="I94" s="15" t="s">
-        <v>889</v>
+        <v>882</v>
       </c>
       <c r="J94" t="s">
         <v>45</v>
@@ -8889,36 +9002,36 @@
         <v>125</v>
       </c>
       <c r="M94" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
     </row>
     <row r="95" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="B95" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="C95" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="D95" t="s">
         <v>105</v>
       </c>
       <c r="E95" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="F95" t="s">
-        <v>601</v>
+        <v>594</v>
       </c>
       <c r="G95" t="s">
         <v>44</v>
       </c>
       <c r="H95" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I95" s="13" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="J95" t="s">
         <v>45</v>
@@ -8930,36 +9043,36 @@
         <v>110</v>
       </c>
       <c r="M95" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
     </row>
     <row r="96" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="B96" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="C96" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="D96" t="s">
         <v>105</v>
       </c>
       <c r="E96" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
       <c r="F96" t="s">
-        <v>606</v>
+        <v>599</v>
       </c>
       <c r="G96" t="s">
         <v>62</v>
       </c>
       <c r="H96" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I96" s="13" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="J96" t="s">
         <v>45</v>
@@ -8971,36 +9084,36 @@
         <v>118</v>
       </c>
       <c r="M96" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
     </row>
     <row r="97" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="B97" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="C97" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="D97" t="s">
         <v>105</v>
       </c>
       <c r="E97" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="F97" t="s">
-        <v>611</v>
+        <v>604</v>
       </c>
       <c r="G97" t="s">
         <v>62</v>
       </c>
       <c r="H97" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I97" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="J97" t="s">
         <v>45</v>
@@ -9012,36 +9125,36 @@
         <v>125</v>
       </c>
       <c r="M97" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
     </row>
     <row r="98" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="B98" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="C98" s="16" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="D98" t="s">
         <v>105</v>
       </c>
       <c r="E98" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="F98" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="G98" t="s">
         <v>62</v>
       </c>
       <c r="H98" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I98" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="J98" t="s">
         <v>45</v>
@@ -9053,36 +9166,36 @@
         <v>110</v>
       </c>
       <c r="M98" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
     </row>
     <row r="99" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="B99" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="C99" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="D99" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="E99" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
       <c r="F99" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
       <c r="G99" t="s">
         <v>62</v>
       </c>
       <c r="H99" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I99" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="J99" t="s">
         <v>45</v>
@@ -9094,36 +9207,36 @@
         <v>118</v>
       </c>
       <c r="M99" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
     </row>
     <row r="100" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="B100" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="C100" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
       <c r="D100" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="E100" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="F100" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="G100" t="s">
         <v>93</v>
       </c>
       <c r="H100" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I100" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
       <c r="J100" t="s">
         <v>45</v>
@@ -9135,36 +9248,36 @@
         <v>125</v>
       </c>
       <c r="M100" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
     </row>
     <row r="101" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="B101" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="C101" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="D101" t="s">
         <v>105</v>
       </c>
       <c r="E101" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
       <c r="F101" t="s">
-        <v>631</v>
+        <v>624</v>
       </c>
       <c r="G101" t="s">
         <v>62</v>
       </c>
       <c r="H101" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="I101" t="s">
-        <v>632</v>
+        <v>625</v>
       </c>
       <c r="J101" t="s">
         <v>45</v>
@@ -9176,36 +9289,36 @@
         <v>110</v>
       </c>
       <c r="M101" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
     </row>
     <row r="102" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>633</v>
+        <v>626</v>
       </c>
       <c r="B102" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="C102" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
       <c r="D102" t="s">
         <v>105</v>
       </c>
       <c r="E102" t="s">
-        <v>635</v>
+        <v>628</v>
       </c>
       <c r="F102" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
       <c r="G102" t="s">
         <v>93</v>
       </c>
       <c r="H102" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="I102" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
       <c r="J102" t="s">
         <v>45</v>
@@ -9217,36 +9330,36 @@
         <v>118</v>
       </c>
       <c r="M102" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
     </row>
     <row r="103" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="B103" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="C103" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="D103" t="s">
         <v>105</v>
       </c>
       <c r="E103" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
       <c r="F103" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
       <c r="G103" t="s">
         <v>44</v>
       </c>
       <c r="H103" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="I103" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
       <c r="J103" t="s">
         <v>45</v>
@@ -9258,36 +9371,36 @@
         <v>125</v>
       </c>
       <c r="M103" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
     </row>
     <row r="104" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
       <c r="B104" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="C104" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="D104" t="s">
         <v>105</v>
       </c>
       <c r="E104" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="F104" t="s">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="G104" t="s">
         <v>44</v>
       </c>
       <c r="H104" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I104" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="J104" t="s">
         <v>45</v>
@@ -9299,36 +9412,36 @@
         <v>110</v>
       </c>
       <c r="M104" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
     </row>
     <row r="105" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="B105" t="s">
-        <v>582</v>
-      </c>
-      <c r="C105" t="s">
-        <v>649</v>
+        <v>576</v>
+      </c>
+      <c r="C105" s="14" t="s">
+        <v>642</v>
       </c>
       <c r="D105" t="s">
         <v>105</v>
       </c>
       <c r="E105" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="F105" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="G105" t="s">
         <v>62</v>
       </c>
       <c r="H105" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="I105" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
       <c r="J105" t="s">
         <v>45</v>
@@ -9340,36 +9453,36 @@
         <v>118</v>
       </c>
       <c r="M105" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
     </row>
     <row r="106" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="B106" t="s">
-        <v>582</v>
-      </c>
-      <c r="C106" t="s">
-        <v>654</v>
+        <v>576</v>
+      </c>
+      <c r="C106" s="14" t="s">
+        <v>647</v>
       </c>
       <c r="D106" t="s">
         <v>105</v>
       </c>
       <c r="E106" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="F106" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="G106" t="s">
         <v>62</v>
       </c>
       <c r="H106" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="I106" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
       <c r="J106" t="s">
         <v>45</v>
@@ -9381,27 +9494,27 @@
         <v>125</v>
       </c>
       <c r="M106" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
     </row>
     <row r="107" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
       <c r="B107" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="C107" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="D107" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="E107" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
       <c r="F107" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="G107" t="s">
         <v>44</v>
@@ -9410,7 +9523,7 @@
         <v>108</v>
       </c>
       <c r="I107" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="J107" t="s">
         <v>45</v>
@@ -9422,27 +9535,27 @@
         <v>110</v>
       </c>
       <c r="M107" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
     </row>
     <row r="108" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="B108" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="C108" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="D108" t="s">
+        <v>654</v>
+      </c>
+      <c r="E108" t="s">
         <v>661</v>
       </c>
-      <c r="E108" t="s">
-        <v>668</v>
-      </c>
       <c r="F108" t="s">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="G108" t="s">
         <v>44</v>
@@ -9451,7 +9564,7 @@
         <v>116</v>
       </c>
       <c r="I108" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="J108" t="s">
         <v>45</v>
@@ -9463,27 +9576,27 @@
         <v>118</v>
       </c>
       <c r="M108" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
     </row>
     <row r="109" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="B109" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="C109" t="s">
-        <v>672</v>
+        <v>665</v>
       </c>
       <c r="D109" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="E109" t="s">
-        <v>673</v>
+        <v>666</v>
       </c>
       <c r="F109" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="G109" t="s">
         <v>44</v>
@@ -9492,7 +9605,7 @@
         <v>123</v>
       </c>
       <c r="I109" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="J109" t="s">
         <v>45</v>
@@ -9504,36 +9617,36 @@
         <v>125</v>
       </c>
       <c r="M109" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
     </row>
     <row r="110" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>676</v>
+        <v>669</v>
       </c>
       <c r="B110" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="C110" t="s">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="D110" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="E110" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="F110" t="s">
-        <v>679</v>
+        <v>672</v>
       </c>
       <c r="G110" t="s">
         <v>44</v>
       </c>
       <c r="H110" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I110" t="s">
-        <v>680</v>
+        <v>673</v>
       </c>
       <c r="J110" t="s">
         <v>45</v>
@@ -9545,36 +9658,36 @@
         <v>110</v>
       </c>
       <c r="M110" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
     </row>
     <row r="111" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="B111" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="C111" t="s">
-        <v>682</v>
+        <v>675</v>
       </c>
       <c r="D111" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="E111" t="s">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="F111" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="G111" t="s">
         <v>62</v>
       </c>
       <c r="H111" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I111" t="s">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="J111" t="s">
         <v>45</v>
@@ -9586,36 +9699,36 @@
         <v>118</v>
       </c>
       <c r="M111" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
     </row>
     <row r="112" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
       <c r="B112" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="C112" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="D112" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="E112" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="F112" t="s">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="G112" t="s">
         <v>62</v>
       </c>
       <c r="H112" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I112" t="s">
-        <v>690</v>
+        <v>683</v>
       </c>
       <c r="J112" t="s">
         <v>45</v>
@@ -9627,36 +9740,36 @@
         <v>125</v>
       </c>
       <c r="M112" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
     </row>
     <row r="113" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>691</v>
+        <v>684</v>
       </c>
       <c r="B113" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="C113" t="s">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="D113" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="E113" t="s">
-        <v>693</v>
+        <v>686</v>
       </c>
       <c r="F113" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="G113" t="s">
         <v>62</v>
       </c>
       <c r="H113" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I113" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="J113" t="s">
         <v>45</v>
@@ -9668,36 +9781,36 @@
         <v>110</v>
       </c>
       <c r="M113" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
     </row>
     <row r="114" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="B114" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="C114" t="s">
-        <v>697</v>
+        <v>690</v>
       </c>
       <c r="D114" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="E114" t="s">
-        <v>698</v>
+        <v>691</v>
       </c>
       <c r="F114" t="s">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="G114" t="s">
         <v>44</v>
       </c>
       <c r="H114" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I114" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="J114" t="s">
         <v>45</v>
@@ -9709,36 +9822,36 @@
         <v>118</v>
       </c>
       <c r="M114" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
     </row>
     <row r="115" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="B115" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="C115" t="s">
-        <v>702</v>
+        <v>695</v>
       </c>
       <c r="D115" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="E115" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="F115" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="G115" t="s">
         <v>44</v>
       </c>
       <c r="H115" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I115" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="J115" t="s">
         <v>45</v>
@@ -9750,36 +9863,36 @@
         <v>125</v>
       </c>
       <c r="M115" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
     </row>
     <row r="116" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="B116" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="C116" t="s">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="D116" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="E116" t="s">
-        <v>708</v>
+        <v>701</v>
       </c>
       <c r="F116" t="s">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="G116" t="s">
         <v>44</v>
       </c>
       <c r="H116" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="I116" t="s">
-        <v>710</v>
+        <v>703</v>
       </c>
       <c r="J116" t="s">
         <v>45</v>
@@ -9791,36 +9904,36 @@
         <v>110</v>
       </c>
       <c r="M116" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
     </row>
     <row r="117" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="B117" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="C117" t="s">
-        <v>712</v>
+        <v>705</v>
       </c>
       <c r="D117" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="E117" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
       <c r="F117" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="G117" t="s">
         <v>44</v>
       </c>
       <c r="H117" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="I117" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="J117" t="s">
         <v>45</v>
@@ -9832,36 +9945,36 @@
         <v>118</v>
       </c>
       <c r="M117" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
     </row>
     <row r="118" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="B118" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="C118" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="D118" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="E118" t="s">
-        <v>718</v>
+        <v>711</v>
       </c>
       <c r="F118" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="G118" t="s">
         <v>44</v>
       </c>
       <c r="H118" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="I118" t="s">
-        <v>720</v>
+        <v>713</v>
       </c>
       <c r="J118" t="s">
         <v>45</v>
@@ -9873,36 +9986,36 @@
         <v>125</v>
       </c>
       <c r="M118" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
     </row>
     <row r="119" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="B119" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="C119" t="s">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="D119" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="E119" t="s">
-        <v>723</v>
+        <v>716</v>
       </c>
       <c r="F119" t="s">
-        <v>724</v>
+        <v>717</v>
       </c>
       <c r="G119" t="s">
         <v>44</v>
       </c>
       <c r="H119" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I119" t="s">
-        <v>725</v>
+        <v>718</v>
       </c>
       <c r="J119" t="s">
         <v>45</v>
@@ -9914,36 +10027,36 @@
         <v>110</v>
       </c>
       <c r="M119" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
     </row>
     <row r="120" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
       <c r="B120" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="C120" t="s">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="D120" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="E120" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
       <c r="F120" t="s">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="G120" t="s">
         <v>62</v>
       </c>
       <c r="H120" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="I120" t="s">
-        <v>730</v>
+        <v>723</v>
       </c>
       <c r="J120" t="s">
         <v>45</v>
@@ -9955,36 +10068,36 @@
         <v>118</v>
       </c>
       <c r="M120" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
     </row>
     <row r="121" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>731</v>
+        <v>724</v>
       </c>
       <c r="B121" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="C121" t="s">
-        <v>732</v>
+        <v>725</v>
       </c>
       <c r="D121" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="E121" t="s">
-        <v>733</v>
+        <v>726</v>
       </c>
       <c r="F121" t="s">
-        <v>734</v>
+        <v>727</v>
       </c>
       <c r="G121" t="s">
         <v>44</v>
       </c>
       <c r="H121" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="I121" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="J121" t="s">
         <v>45</v>
@@ -9996,27 +10109,27 @@
         <v>125</v>
       </c>
       <c r="M121" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
     </row>
     <row r="122" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="B122" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="C122" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="D122" t="s">
         <v>105</v>
       </c>
       <c r="E122" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="F122" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="G122" t="s">
         <v>44</v>
@@ -10025,7 +10138,7 @@
         <v>108</v>
       </c>
       <c r="I122" t="s">
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="J122" t="s">
         <v>45</v>
@@ -10037,27 +10150,27 @@
         <v>110</v>
       </c>
       <c r="M122" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
     </row>
     <row r="123" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="B123" t="s">
+        <v>730</v>
+      </c>
+      <c r="C123" t="s">
         <v>737</v>
-      </c>
-      <c r="C123" t="s">
-        <v>744</v>
       </c>
       <c r="D123" t="s">
         <v>105</v>
       </c>
       <c r="E123" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="F123" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="G123" t="s">
         <v>44</v>
@@ -10066,7 +10179,7 @@
         <v>116</v>
       </c>
       <c r="I123" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="J123" t="s">
         <v>45</v>
@@ -10078,27 +10191,27 @@
         <v>118</v>
       </c>
       <c r="M123" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
     </row>
     <row r="124" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="B124" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="C124" t="s">
-        <v>749</v>
+        <v>742</v>
       </c>
       <c r="D124" t="s">
         <v>105</v>
       </c>
       <c r="E124" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="F124" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
       <c r="G124" t="s">
         <v>44</v>
@@ -10107,7 +10220,7 @@
         <v>123</v>
       </c>
       <c r="I124" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="J124" t="s">
         <v>45</v>
@@ -10119,36 +10232,36 @@
         <v>125</v>
       </c>
       <c r="M124" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
     </row>
     <row r="125" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="B125" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="C125" t="s">
-        <v>754</v>
+        <v>747</v>
       </c>
       <c r="D125" t="s">
         <v>105</v>
       </c>
       <c r="E125" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="F125" t="s">
-        <v>756</v>
+        <v>749</v>
       </c>
       <c r="G125" t="s">
         <v>62</v>
       </c>
       <c r="H125" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I125" t="s">
-        <v>757</v>
+        <v>750</v>
       </c>
       <c r="J125" t="s">
         <v>45</v>
@@ -10160,36 +10273,36 @@
         <v>110</v>
       </c>
       <c r="M125" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
     </row>
     <row r="126" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="B126" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="C126" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="D126" t="s">
         <v>105</v>
       </c>
       <c r="E126" t="s">
-        <v>760</v>
+        <v>753</v>
       </c>
       <c r="F126" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
       <c r="G126" t="s">
         <v>44</v>
       </c>
       <c r="H126" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I126" t="s">
-        <v>762</v>
+        <v>755</v>
       </c>
       <c r="J126" t="s">
         <v>45</v>
@@ -10201,36 +10314,36 @@
         <v>118</v>
       </c>
       <c r="M126" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
     </row>
     <row r="127" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>763</v>
+        <v>756</v>
       </c>
       <c r="B127" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="C127" t="s">
-        <v>764</v>
+        <v>757</v>
       </c>
       <c r="D127" t="s">
         <v>105</v>
       </c>
       <c r="E127" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="F127" t="s">
-        <v>766</v>
+        <v>759</v>
       </c>
       <c r="G127" t="s">
         <v>44</v>
       </c>
       <c r="H127" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I127" t="s">
-        <v>767</v>
+        <v>760</v>
       </c>
       <c r="J127" t="s">
         <v>45</v>
@@ -10242,36 +10355,36 @@
         <v>125</v>
       </c>
       <c r="M127" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
     </row>
     <row r="128" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>768</v>
+        <v>761</v>
       </c>
       <c r="B128" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="C128" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="D128" t="s">
         <v>105</v>
       </c>
       <c r="E128" t="s">
-        <v>770</v>
+        <v>763</v>
       </c>
       <c r="F128" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
       <c r="G128" t="s">
         <v>44</v>
       </c>
       <c r="H128" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I128" t="s">
-        <v>772</v>
+        <v>765</v>
       </c>
       <c r="J128" t="s">
         <v>45</v>
@@ -10283,36 +10396,36 @@
         <v>110</v>
       </c>
       <c r="M128" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
     </row>
     <row r="129" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="B129" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="C129" t="s">
-        <v>774</v>
+        <v>767</v>
       </c>
       <c r="D129" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="E129" t="s">
-        <v>775</v>
+        <v>768</v>
       </c>
       <c r="F129" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="G129" t="s">
         <v>62</v>
       </c>
       <c r="H129" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I129" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="J129" t="s">
         <v>45</v>
@@ -10324,36 +10437,36 @@
         <v>118</v>
       </c>
       <c r="M129" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
     </row>
     <row r="130" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="B130" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="C130" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="D130" t="s">
         <v>105</v>
       </c>
       <c r="E130" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="F130" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="G130" t="s">
         <v>44</v>
       </c>
       <c r="H130" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I130" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="J130" t="s">
         <v>45</v>
@@ -10365,36 +10478,36 @@
         <v>125</v>
       </c>
       <c r="M130" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
     </row>
     <row r="131" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="B131" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="C131" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="D131" t="s">
         <v>105</v>
       </c>
       <c r="E131" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="F131" t="s">
-        <v>786</v>
+        <v>779</v>
       </c>
       <c r="G131" t="s">
         <v>44</v>
       </c>
       <c r="H131" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="I131" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
       <c r="J131" t="s">
         <v>45</v>
@@ -10406,36 +10519,36 @@
         <v>110</v>
       </c>
       <c r="M131" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
     </row>
     <row r="132" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B132" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="C132" t="s">
-        <v>789</v>
+        <v>782</v>
       </c>
       <c r="D132" t="s">
         <v>105</v>
       </c>
       <c r="E132" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="F132" t="s">
-        <v>791</v>
+        <v>784</v>
       </c>
       <c r="G132" t="s">
         <v>62</v>
       </c>
       <c r="H132" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="I132" t="s">
-        <v>792</v>
+        <v>785</v>
       </c>
       <c r="J132" t="s">
         <v>45</v>
@@ -10447,36 +10560,36 @@
         <v>118</v>
       </c>
       <c r="M132" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
     </row>
     <row r="133" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>793</v>
+        <v>786</v>
       </c>
       <c r="B133" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="C133" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="D133" t="s">
         <v>105</v>
       </c>
       <c r="E133" t="s">
-        <v>795</v>
+        <v>788</v>
       </c>
       <c r="F133" t="s">
-        <v>796</v>
+        <v>789</v>
       </c>
       <c r="G133" t="s">
         <v>93</v>
       </c>
       <c r="H133" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="I133" t="s">
-        <v>797</v>
+        <v>790</v>
       </c>
       <c r="J133" t="s">
         <v>45</v>
@@ -10488,36 +10601,36 @@
         <v>125</v>
       </c>
       <c r="M133" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
     </row>
     <row r="134" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>798</v>
+        <v>791</v>
       </c>
       <c r="B134" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="C134" t="s">
-        <v>799</v>
+        <v>792</v>
       </c>
       <c r="D134" t="s">
         <v>105</v>
       </c>
       <c r="E134" t="s">
-        <v>800</v>
+        <v>793</v>
       </c>
       <c r="F134" t="s">
-        <v>801</v>
+        <v>794</v>
       </c>
       <c r="G134" t="s">
         <v>44</v>
       </c>
       <c r="H134" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I134" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
       <c r="J134" t="s">
         <v>45</v>
@@ -10529,36 +10642,36 @@
         <v>110</v>
       </c>
       <c r="M134" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
     </row>
     <row r="135" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="B135" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="C135" t="s">
-        <v>804</v>
+        <v>797</v>
       </c>
       <c r="D135" t="s">
         <v>105</v>
       </c>
       <c r="E135" t="s">
-        <v>805</v>
+        <v>798</v>
       </c>
       <c r="F135" t="s">
-        <v>806</v>
+        <v>799</v>
       </c>
       <c r="G135" t="s">
         <v>44</v>
       </c>
       <c r="H135" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="I135" t="s">
-        <v>807</v>
+        <v>800</v>
       </c>
       <c r="J135" t="s">
         <v>45</v>
@@ -10570,36 +10683,36 @@
         <v>118</v>
       </c>
       <c r="M135" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
     </row>
     <row r="136" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>808</v>
+        <v>801</v>
       </c>
       <c r="B136" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="C136" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="D136" t="s">
         <v>105</v>
       </c>
       <c r="E136" t="s">
-        <v>810</v>
+        <v>803</v>
       </c>
       <c r="F136" t="s">
-        <v>811</v>
+        <v>804</v>
       </c>
       <c r="G136" t="s">
         <v>62</v>
       </c>
       <c r="H136" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="I136" t="s">
-        <v>812</v>
+        <v>805</v>
       </c>
       <c r="J136" t="s">
         <v>45</v>
@@ -10611,27 +10724,27 @@
         <v>125</v>
       </c>
       <c r="M136" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
     </row>
     <row r="137" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>813</v>
+        <v>806</v>
       </c>
       <c r="B137" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
       <c r="C137" t="s">
-        <v>815</v>
+        <v>808</v>
       </c>
       <c r="D137" t="s">
         <v>105</v>
       </c>
       <c r="E137" t="s">
-        <v>816</v>
+        <v>809</v>
       </c>
       <c r="F137" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="G137" t="s">
         <v>44</v>
@@ -10640,7 +10753,7 @@
         <v>108</v>
       </c>
       <c r="I137" t="s">
-        <v>818</v>
+        <v>811</v>
       </c>
       <c r="J137" t="s">
         <v>45</v>
@@ -10652,27 +10765,27 @@
         <v>110</v>
       </c>
       <c r="M137" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
     </row>
     <row r="138" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>820</v>
+        <v>813</v>
       </c>
       <c r="B138" t="s">
+        <v>807</v>
+      </c>
+      <c r="C138" t="s">
         <v>814</v>
-      </c>
-      <c r="C138" t="s">
-        <v>821</v>
       </c>
       <c r="D138" t="s">
         <v>105</v>
       </c>
       <c r="E138" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
       <c r="F138" t="s">
-        <v>823</v>
+        <v>816</v>
       </c>
       <c r="G138" t="s">
         <v>44</v>
@@ -10681,7 +10794,7 @@
         <v>116</v>
       </c>
       <c r="I138" t="s">
-        <v>824</v>
+        <v>817</v>
       </c>
       <c r="J138" t="s">
         <v>45</v>
@@ -10693,27 +10806,27 @@
         <v>118</v>
       </c>
       <c r="M138" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
     </row>
     <row r="139" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
       <c r="B139" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
       <c r="C139" t="s">
-        <v>826</v>
+        <v>819</v>
       </c>
       <c r="D139" t="s">
         <v>105</v>
       </c>
       <c r="E139" t="s">
-        <v>827</v>
+        <v>820</v>
       </c>
       <c r="F139" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
       <c r="G139" t="s">
         <v>62</v>
@@ -10722,7 +10835,7 @@
         <v>123</v>
       </c>
       <c r="I139" t="s">
-        <v>829</v>
+        <v>822</v>
       </c>
       <c r="J139" t="s">
         <v>45</v>
@@ -10734,36 +10847,36 @@
         <v>125</v>
       </c>
       <c r="M139" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
     </row>
     <row r="140" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>830</v>
+        <v>823</v>
       </c>
       <c r="B140" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
       <c r="C140" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="D140" t="s">
         <v>105</v>
       </c>
       <c r="E140" t="s">
-        <v>832</v>
+        <v>825</v>
       </c>
       <c r="F140" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="G140" t="s">
         <v>44</v>
       </c>
       <c r="H140" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I140" t="s">
-        <v>834</v>
+        <v>827</v>
       </c>
       <c r="J140" t="s">
         <v>45</v>
@@ -10775,36 +10888,36 @@
         <v>110</v>
       </c>
       <c r="M140" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
     </row>
     <row r="141" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>835</v>
+        <v>828</v>
       </c>
       <c r="B141" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
       <c r="C141" t="s">
-        <v>836</v>
+        <v>829</v>
       </c>
       <c r="D141" t="s">
         <v>105</v>
       </c>
       <c r="E141" t="s">
-        <v>837</v>
+        <v>830</v>
       </c>
       <c r="F141" t="s">
-        <v>838</v>
+        <v>831</v>
       </c>
       <c r="G141" t="s">
         <v>62</v>
       </c>
       <c r="H141" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I141" t="s">
-        <v>839</v>
+        <v>832</v>
       </c>
       <c r="J141" t="s">
         <v>45</v>
@@ -10816,36 +10929,36 @@
         <v>118</v>
       </c>
       <c r="M141" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
     </row>
     <row r="142" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
       <c r="B142" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
       <c r="C142" t="s">
-        <v>841</v>
+        <v>834</v>
       </c>
       <c r="D142" t="s">
         <v>105</v>
       </c>
       <c r="E142" t="s">
-        <v>842</v>
+        <v>835</v>
       </c>
       <c r="F142" t="s">
-        <v>843</v>
+        <v>836</v>
       </c>
       <c r="G142" t="s">
         <v>44</v>
       </c>
       <c r="H142" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I142" t="s">
-        <v>844</v>
+        <v>837</v>
       </c>
       <c r="J142" t="s">
         <v>45</v>
@@ -10857,36 +10970,36 @@
         <v>125</v>
       </c>
       <c r="M142" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
     </row>
     <row r="143" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>845</v>
+        <v>838</v>
       </c>
       <c r="B143" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
       <c r="C143" t="s">
-        <v>846</v>
+        <v>839</v>
       </c>
       <c r="D143" t="s">
         <v>105</v>
       </c>
       <c r="E143" t="s">
-        <v>847</v>
+        <v>840</v>
       </c>
       <c r="F143" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="G143" t="s">
         <v>44</v>
       </c>
       <c r="H143" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I143" t="s">
-        <v>848</v>
+        <v>841</v>
       </c>
       <c r="J143" t="s">
         <v>45</v>
@@ -10898,36 +11011,36 @@
         <v>110</v>
       </c>
       <c r="M143" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
     </row>
     <row r="144" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>849</v>
+        <v>842</v>
       </c>
       <c r="B144" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
       <c r="C144" t="s">
-        <v>850</v>
+        <v>843</v>
       </c>
       <c r="D144" t="s">
         <v>105</v>
       </c>
       <c r="E144" t="s">
-        <v>851</v>
+        <v>844</v>
       </c>
       <c r="F144" t="s">
-        <v>852</v>
+        <v>845</v>
       </c>
       <c r="G144" t="s">
         <v>44</v>
       </c>
       <c r="H144" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I144" t="s">
-        <v>853</v>
+        <v>846</v>
       </c>
       <c r="J144" t="s">
         <v>45</v>
@@ -10939,36 +11052,36 @@
         <v>118</v>
       </c>
       <c r="M144" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
     </row>
     <row r="145" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>854</v>
+        <v>847</v>
       </c>
       <c r="B145" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
       <c r="C145" t="s">
-        <v>855</v>
+        <v>848</v>
       </c>
       <c r="D145" t="s">
         <v>105</v>
       </c>
       <c r="E145" t="s">
-        <v>856</v>
+        <v>849</v>
       </c>
       <c r="F145" t="s">
-        <v>857</v>
+        <v>850</v>
       </c>
       <c r="G145" t="s">
         <v>93</v>
       </c>
       <c r="H145" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I145" t="s">
-        <v>858</v>
+        <v>851</v>
       </c>
       <c r="J145" t="s">
         <v>45</v>
@@ -10980,36 +11093,36 @@
         <v>125</v>
       </c>
       <c r="M145" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
     </row>
     <row r="146" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>859</v>
+        <v>852</v>
       </c>
       <c r="B146" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
       <c r="C146" t="s">
-        <v>860</v>
+        <v>853</v>
       </c>
       <c r="D146" t="s">
         <v>105</v>
       </c>
       <c r="E146" t="s">
-        <v>861</v>
+        <v>854</v>
       </c>
       <c r="F146" t="s">
-        <v>862</v>
+        <v>855</v>
       </c>
       <c r="G146" t="s">
         <v>62</v>
       </c>
       <c r="H146" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="I146" t="s">
-        <v>863</v>
+        <v>856</v>
       </c>
       <c r="J146" t="s">
         <v>45</v>
@@ -11021,36 +11134,36 @@
         <v>110</v>
       </c>
       <c r="M146" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
     </row>
     <row r="147" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>864</v>
+        <v>857</v>
       </c>
       <c r="B147" t="s">
-        <v>814</v>
-      </c>
-      <c r="C147" t="s">
-        <v>865</v>
+        <v>807</v>
+      </c>
+      <c r="C147" s="14" t="s">
+        <v>858</v>
       </c>
       <c r="D147" t="s">
         <v>105</v>
       </c>
       <c r="E147" t="s">
-        <v>866</v>
+        <v>859</v>
       </c>
       <c r="F147" t="s">
-        <v>867</v>
+        <v>860</v>
       </c>
       <c r="G147" t="s">
         <v>62</v>
       </c>
       <c r="H147" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="I147" t="s">
-        <v>868</v>
+        <v>861</v>
       </c>
       <c r="J147" t="s">
         <v>45</v>
@@ -11062,36 +11175,36 @@
         <v>118</v>
       </c>
       <c r="M147" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
     </row>
     <row r="148" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>869</v>
+        <v>862</v>
       </c>
       <c r="B148" t="s">
-        <v>814</v>
-      </c>
-      <c r="C148" t="s">
-        <v>870</v>
+        <v>807</v>
+      </c>
+      <c r="C148" s="14" t="s">
+        <v>863</v>
       </c>
       <c r="D148" t="s">
         <v>105</v>
       </c>
       <c r="E148" t="s">
-        <v>871</v>
+        <v>864</v>
       </c>
       <c r="F148" t="s">
-        <v>872</v>
+        <v>865</v>
       </c>
       <c r="G148" t="s">
         <v>44</v>
       </c>
       <c r="H148" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="I148" t="s">
-        <v>873</v>
+        <v>866</v>
       </c>
       <c r="J148" t="s">
         <v>45</v>
@@ -11103,36 +11216,36 @@
         <v>125</v>
       </c>
       <c r="M148" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
     </row>
     <row r="149" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="B149" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
       <c r="C149" t="s">
-        <v>875</v>
+        <v>868</v>
       </c>
       <c r="D149" t="s">
         <v>105</v>
       </c>
       <c r="E149" t="s">
-        <v>876</v>
+        <v>869</v>
       </c>
       <c r="F149" t="s">
-        <v>877</v>
+        <v>870</v>
       </c>
       <c r="G149" t="s">
         <v>44</v>
       </c>
       <c r="H149" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I149" t="s">
-        <v>878</v>
+        <v>871</v>
       </c>
       <c r="J149" t="s">
         <v>45</v>
@@ -11144,36 +11257,36 @@
         <v>110</v>
       </c>
       <c r="M149" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
     </row>
     <row r="150" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>879</v>
+        <v>872</v>
       </c>
       <c r="B150" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
       <c r="C150" t="s">
-        <v>880</v>
+        <v>873</v>
       </c>
       <c r="D150" t="s">
         <v>105</v>
       </c>
       <c r="E150" t="s">
-        <v>881</v>
+        <v>874</v>
       </c>
       <c r="F150" t="s">
-        <v>882</v>
+        <v>875</v>
       </c>
       <c r="G150" t="s">
         <v>44</v>
       </c>
       <c r="H150" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="I150" t="s">
-        <v>883</v>
+        <v>876</v>
       </c>
       <c r="J150" t="s">
         <v>45</v>
@@ -11185,36 +11298,36 @@
         <v>118</v>
       </c>
       <c r="M150" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
     </row>
     <row r="151" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>884</v>
+        <v>877</v>
       </c>
       <c r="B151" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
       <c r="C151" t="s">
-        <v>885</v>
+        <v>878</v>
       </c>
       <c r="D151" t="s">
         <v>105</v>
       </c>
       <c r="E151" t="s">
-        <v>886</v>
+        <v>879</v>
       </c>
       <c r="F151" t="s">
-        <v>887</v>
+        <v>880</v>
       </c>
       <c r="G151" t="s">
         <v>93</v>
       </c>
       <c r="H151" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="I151" t="s">
-        <v>888</v>
+        <v>881</v>
       </c>
       <c r="J151" t="s">
         <v>45</v>
@@ -11226,7 +11339,7 @@
         <v>125</v>
       </c>
       <c r="M151" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
     </row>
     <row r="152" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
